--- a/Team-Data/2014-15/2-2-2014-15.xlsx
+++ b/Team-Data/2014-15/2-2-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
@@ -679,7 +746,7 @@
         <v>38.1</v>
       </c>
       <c r="J2" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.472</v>
@@ -688,16 +755,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="O2" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P2" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0.772</v>
@@ -706,16 +773,16 @@
         <v>8.5</v>
       </c>
       <c r="S2" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U2" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="V2" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W2" t="n">
         <v>8.800000000000001</v>
@@ -724,31 +791,31 @@
         <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.3</v>
+        <v>103.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>24</v>
@@ -757,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
         <v>4</v>
@@ -772,10 +839,10 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -784,10 +851,10 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -799,22 +866,22 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
         <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -960,19 +1027,19 @@
         <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
         <v>16</v>
@@ -981,13 +1048,13 @@
         <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -1025,103 +1092,103 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.404</v>
+        <v>0.391</v>
       </c>
       <c r="H4" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J4" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.32</v>
+        <v>0.316</v>
       </c>
       <c r="O4" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.744</v>
+        <v>0.749</v>
       </c>
       <c r="R4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V4" t="n">
         <v>14.4</v>
       </c>
       <c r="W4" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
         <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>23</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>18</v>
@@ -1130,40 +1197,40 @@
         <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1172,7 +1239,7 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.438</v>
+        <v>0.426</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,34 +1292,34 @@
         <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="K5" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
         <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.305</v>
+        <v>0.306</v>
       </c>
       <c r="O5" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0.73</v>
       </c>
       <c r="R5" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S5" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T5" t="n">
         <v>44.1</v>
@@ -1270,25 +1337,25 @@
         <v>5.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
         <v>94.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
         <v>18</v>
@@ -1300,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ5" t="n">
         <v>9</v>
@@ -1318,22 +1385,22 @@
         <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>26</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>10</v>
@@ -1509,7 +1576,7 @@
         <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.592</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J7" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K7" t="n">
         <v>0.453</v>
@@ -1598,19 +1665,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O7" t="n">
         <v>18.4</v>
       </c>
       <c r="P7" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R7" t="n">
         <v>11.4</v>
@@ -1619,16 +1686,16 @@
         <v>31</v>
       </c>
       <c r="T7" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U7" t="n">
         <v>21.5</v>
       </c>
       <c r="V7" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
         <v>4.1</v>
@@ -1637,22 +1704,22 @@
         <v>4.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA7" t="n">
         <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1664,10 +1731,10 @@
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK7" t="n">
         <v>15</v>
@@ -1679,13 +1746,13 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>15</v>
@@ -1694,7 +1761,7 @@
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT7" t="n">
         <v>19</v>
@@ -1703,16 +1770,16 @@
         <v>15</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ7" t="n">
         <v>2</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1823,13 @@
         <v>49</v>
       </c>
       <c r="E8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>0.673</v>
+        <v>0.653</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,49 +1838,49 @@
         <v>40.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
       </c>
       <c r="L8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O8" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P8" t="n">
         <v>22.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
         <v>10.6</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W8" t="n">
         <v>8.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1822,25 +1889,25 @@
         <v>19.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB8" t="n">
         <v>106.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>14</v>
@@ -1861,22 +1928,22 @@
         <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2022,7 +2089,7 @@
         <v>20</v>
       </c>
       <c r="AG9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
         <v>16</v>
@@ -2043,7 +2110,7 @@
         <v>12</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
@@ -2067,7 +2134,7 @@
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
         <v>26</v>
@@ -2082,7 +2149,7 @@
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -2195,10 +2262,10 @@
         <v>-2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="n">
         <v>22</v>
@@ -2210,7 +2277,7 @@
         <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
         <v>6</v>
@@ -2222,13 +2289,13 @@
         <v>10</v>
       </c>
       <c r="AM10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN10" t="n">
         <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
         <v>15</v>
@@ -2240,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>3</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -2255,16 +2322,16 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -2404,13 +2471,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
         <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="n">
         <v>23</v>
@@ -2419,7 +2486,7 @@
         <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.681</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O12" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
         <v>21.3</v>
@@ -2538,31 +2605,31 @@
         <v>17.3</v>
       </c>
       <c r="W12" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
@@ -2571,13 +2638,13 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
         <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
@@ -2589,52 +2656,52 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
         <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX12" t="n">
         <v>20</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-2</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2759,7 +2826,7 @@
         <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2768,19 +2835,19 @@
         <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="n">
         <v>25</v>
       </c>
       <c r="AO13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
         <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>15</v>
@@ -2801,7 +2868,7 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -2845,94 +2912,94 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
         <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.673</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J14" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="P14" t="n">
         <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.741</v>
+        <v>0.75</v>
       </c>
       <c r="R14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T14" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.7</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD14" t="n">
         <v>7</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2944,7 +3011,7 @@
         <v>19</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>4</v>
@@ -2953,22 +3020,22 @@
         <v>6</v>
       </c>
       <c r="AN14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO14" t="n">
         <v>4</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT14" t="n">
         <v>24</v>
@@ -2983,7 +3050,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>0.277</v>
+        <v>0.271</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.434</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M15" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N15" t="n">
         <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P15" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="U15" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V15" t="n">
         <v>13.1</v>
@@ -3093,19 +3160,19 @@
         <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,16 +3184,16 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
         <v>23</v>
@@ -3135,25 +3202,25 @@
         <v>23</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AP15" t="n">
         <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>23</v>
@@ -3162,7 +3229,7 @@
         <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
@@ -3171,10 +3238,10 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -3209,58 +3276,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.75</v>
+        <v>0.745</v>
       </c>
       <c r="H16" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I16" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J16" t="n">
         <v>83.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L16" t="n">
         <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P16" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
         <v>0.778</v>
       </c>
       <c r="R16" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S16" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T16" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U16" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V16" t="n">
         <v>13</v>
@@ -3275,7 +3342,7 @@
         <v>5.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA16" t="n">
         <v>20.9</v>
@@ -3284,10 +3351,10 @@
         <v>101.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,16 +3366,16 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3317,31 +3384,31 @@
         <v>28</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3356,13 +3423,13 @@
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB16" t="n">
         <v>12</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3499,7 +3566,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>11</v>
@@ -3508,7 +3575,7 @@
         <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3529,7 +3596,7 @@
         <v>11</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -3573,52 +3640,52 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" t="n">
         <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>0.542</v>
+        <v>0.532</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J18" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.464</v>
+        <v>0.466</v>
       </c>
       <c r="L18" t="n">
         <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O18" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.767</v>
+        <v>0.771</v>
       </c>
       <c r="R18" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S18" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T18" t="n">
         <v>41.3</v>
@@ -3630,7 +3697,7 @@
         <v>17</v>
       </c>
       <c r="W18" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X18" t="n">
         <v>4.7</v>
@@ -3639,34 +3706,34 @@
         <v>4.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA18" t="n">
         <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>14</v>
       </c>
       <c r="AH18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI18" t="n">
         <v>12</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>13</v>
       </c>
       <c r="AJ18" t="n">
         <v>25</v>
@@ -3678,7 +3745,7 @@
         <v>19</v>
       </c>
       <c r="AM18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
         <v>5</v>
@@ -3690,13 +3757,13 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3717,7 +3784,7 @@
         <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
         <v>23</v>
@@ -3726,7 +3793,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.167</v>
+        <v>0.17</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,40 +3840,40 @@
         <v>36.8</v>
       </c>
       <c r="J19" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.435</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M19" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="O19" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P19" t="n">
         <v>24.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.753</v>
+        <v>0.75</v>
       </c>
       <c r="R19" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T19" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V19" t="n">
         <v>15.1</v>
@@ -3818,7 +3885,7 @@
         <v>4.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
         <v>19.4</v>
@@ -3830,10 +3897,10 @@
         <v>97.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.4</v>
+        <v>-9.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3845,7 +3912,7 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>20</v>
@@ -3854,7 +3921,7 @@
         <v>12</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3863,25 +3930,25 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
       </c>
       <c r="AT19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
@@ -3893,13 +3960,13 @@
         <v>7</v>
       </c>
       <c r="AX19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY19" t="n">
         <v>27</v>
       </c>
-      <c r="AY19" t="n">
-        <v>29</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -3952,79 +4019,79 @@
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J20" t="n">
-        <v>83.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O20" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P20" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S20" t="n">
         <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4033,43 +4100,43 @@
         <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO20" t="n">
         <v>15</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>12</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT20" t="n">
         <v>9</v>
       </c>
-      <c r="AR20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10</v>
-      </c>
       <c r="AU20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
@@ -4078,10 +4145,10 @@
         <v>6</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,28 +4386,28 @@
         <v>37.2</v>
       </c>
       <c r="J22" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="K22" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L22" t="n">
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.319</v>
+        <v>0.318</v>
       </c>
       <c r="O22" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P22" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="R22" t="n">
         <v>12</v>
@@ -4349,22 +4416,22 @@
         <v>34.6</v>
       </c>
       <c r="T22" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="U22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W22" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X22" t="n">
         <v>5.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z22" t="n">
         <v>22.5</v>
@@ -4373,13 +4440,13 @@
         <v>19.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>16</v>
@@ -4391,10 +4458,10 @@
         <v>16</v>
       </c>
       <c r="AH22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI22" t="n">
         <v>16</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>18</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
@@ -4409,16 +4476,16 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AP22" t="n">
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
         <v>6</v>
@@ -4433,22 +4500,22 @@
         <v>28</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
         <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -4498,43 +4565,43 @@
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O23" t="n">
         <v>14.5</v>
       </c>
       <c r="P23" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.733</v>
+        <v>0.731</v>
       </c>
       <c r="R23" t="n">
         <v>8.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4543,22 +4610,22 @@
         <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA23" t="n">
         <v>18.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.1</v>
+        <v>-6.3</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4567,19 +4634,19 @@
         <v>26</v>
       </c>
       <c r="AF23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
         <v>11</v>
@@ -4591,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4606,13 +4673,13 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>22</v>
@@ -4633,7 +4700,7 @@
         <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -4665,43 +4732,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
         <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" t="n">
-        <v>0.204</v>
+        <v>0.208</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="J24" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K24" t="n">
         <v>0.409</v>
       </c>
       <c r="L24" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M24" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.303</v>
+        <v>0.302</v>
       </c>
       <c r="O24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P24" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q24" t="n">
         <v>0.6830000000000001</v>
@@ -4710,22 +4777,22 @@
         <v>11.6</v>
       </c>
       <c r="S24" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T24" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U24" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V24" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="W24" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
         <v>5.6</v>
@@ -4737,22 +4804,22 @@
         <v>20.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>89.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-11.6</v>
+        <v>-11.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
@@ -4761,13 +4828,13 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4791,7 +4858,7 @@
         <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
         <v>27</v>
@@ -4800,19 +4867,19 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
         <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
@@ -4868,43 +4935,43 @@
         <v>86.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L25" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="N25" t="n">
         <v>0.359</v>
       </c>
       <c r="O25" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P25" t="n">
         <v>21.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.787</v>
+        <v>0.79</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T25" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U25" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V25" t="n">
         <v>15.1</v>
       </c>
       <c r="W25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
@@ -4913,19 +4980,19 @@
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA25" t="n">
         <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>106.6</v>
+        <v>106.8</v>
       </c>
       <c r="AC25" t="n">
         <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4946,16 +5013,16 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>6</v>
       </c>
       <c r="AM25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
         <v>18</v>
@@ -4970,7 +5037,7 @@
         <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
         <v>18</v>
@@ -5000,7 +5067,7 @@
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
         <v>12</v>
@@ -5161,19 +5228,19 @@
         <v>9</v>
       </c>
       <c r="AV26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW26" t="n">
         <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5334,7 +5401,7 @@
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT27" t="n">
         <v>8</v>
@@ -5355,7 +5422,7 @@
         <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -5393,73 +5460,73 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.617</v>
+        <v>0.625</v>
       </c>
       <c r="H28" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I28" t="n">
         <v>37.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="O28" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="P28" t="n">
         <v>22.4</v>
       </c>
-      <c r="N28" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="O28" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>22.5</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.1</v>
       </c>
       <c r="V28" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA28" t="n">
         <v>20.2</v>
@@ -5468,31 +5535,31 @@
         <v>101</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="n">
         <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
         <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5504,13 +5571,13 @@
         <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,13 +5586,13 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
@@ -5540,13 +5607,13 @@
         <v>11</v>
       </c>
       <c r="BA28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
         <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
         <v>33</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>0.673</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>38.7</v>
+        <v>39</v>
       </c>
       <c r="J29" t="n">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="L29" t="n">
         <v>8.9</v>
@@ -5605,7 +5672,7 @@
         <v>25.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O29" t="n">
         <v>19.9</v>
@@ -5626,43 +5693,43 @@
         <v>41.9</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W29" t="n">
         <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AA29" t="n">
         <v>21.7</v>
       </c>
-      <c r="AA29" t="n">
-        <v>21.6</v>
-      </c>
       <c r="AB29" t="n">
-        <v>106.1</v>
+        <v>106.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
       </c>
       <c r="AF29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH29" t="n">
         <v>7</v>
@@ -5674,7 +5741,7 @@
         <v>11</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5683,7 +5750,7 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5704,7 +5771,7 @@
         <v>21</v>
       </c>
       <c r="AU29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
@@ -5713,13 +5780,13 @@
         <v>16</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
@@ -5728,7 +5795,7 @@
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
@@ -5859,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM30" t="n">
         <v>17</v>
@@ -5868,25 +5935,25 @@
         <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
         <v>26</v>
@@ -5898,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ30" t="n">
         <v>5</v>
@@ -5907,7 +5974,7 @@
         <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
         <v>31</v>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G31" t="n">
-        <v>0.633</v>
+        <v>0.646</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J31" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L31" t="n">
         <v>6.1</v>
@@ -5969,16 +6036,16 @@
         <v>16</v>
       </c>
       <c r="N31" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O31" t="n">
         <v>16.1</v>
       </c>
       <c r="P31" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.741</v>
+        <v>0.739</v>
       </c>
       <c r="R31" t="n">
         <v>10.4</v>
@@ -5990,10 +6057,10 @@
         <v>43.8</v>
       </c>
       <c r="U31" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="V31" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W31" t="n">
         <v>7.5</v>
@@ -6011,19 +6078,19 @@
         <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.90000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>9</v>
       </c>
       <c r="AF31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG31" t="n">
         <v>9</v>
@@ -6035,10 +6102,10 @@
         <v>6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6047,7 +6114,7 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
@@ -6056,22 +6123,22 @@
         <v>22</v>
       </c>
       <c r="AQ31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR31" t="n">
         <v>22</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>21</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>16</v>
@@ -6083,10 +6150,10 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-2-2014-15</t>
+          <t>2015-02-02</t>
         </is>
       </c>
     </row>
